--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_C_VSCOFF-CSTD-0-01-A-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_C_VSCOFF-CSTD-0-01-A-C0.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\shamoto\Sprint62\設計書\scc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\BEV\BEV設計・実装\課題管理一覧\フレーム変更漏れ対応\Alertパラメータ設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D230E7-7AEB-4B5B-85BC-CE7E62BE8839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="930" yWindow="0" windowWidth="24120" windowHeight="12660"/>
+    <workbookView xWindow="25974" yWindow="-109" windowWidth="26301" windowHeight="14305" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -21,17 +22,30 @@
     <sheet name="Reference" sheetId="22" r:id="rId7"/>
     <sheet name="History" sheetId="7" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>YOSHIKI IWATA</author>
   </authors>
   <commentList>
-    <comment ref="B10" authorId="0" shapeId="0">
+    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -48,7 +62,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C12" authorId="0" shapeId="0">
+    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
@@ -65,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E12" authorId="0" shapeId="0">
+    <comment ref="E12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
         <r>
           <rPr>
@@ -85,12 +99,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>鈴木　大助</author>
   </authors>
   <commentList>
-    <comment ref="C3" authorId="0" shapeId="0">
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
@@ -136,7 +150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P3" authorId="0" shapeId="0">
+    <comment ref="P3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
@@ -152,7 +166,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="0" shapeId="0">
+    <comment ref="Q3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <r>
           <rPr>
@@ -170,7 +184,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P33" authorId="0" shapeId="0">
+    <comment ref="P33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <r>
           <rPr>
@@ -186,7 +200,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q33" authorId="0" shapeId="0">
+    <comment ref="Q33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <r>
           <rPr>
@@ -207,13 +221,13 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>鈴木　大助</author>
     <author>YOSHIKI IWATA</author>
   </authors>
   <commentList>
-    <comment ref="E2" authorId="0" shapeId="0">
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
       <text>
         <r>
           <rPr>
@@ -228,7 +242,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F2" authorId="1" shapeId="0">
+    <comment ref="F2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000002000000}">
       <text>
         <r>
           <rPr>
@@ -256,7 +270,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G2" authorId="0" shapeId="0">
+    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000003000000}">
       <text>
         <r>
           <rPr>
@@ -271,7 +285,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H2" authorId="0" shapeId="0">
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000004000000}">
       <text>
         <r>
           <rPr>
@@ -292,7 +306,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I2" authorId="0" shapeId="0">
+    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000005000000}">
       <text>
         <r>
           <rPr>
@@ -307,7 +321,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J2" authorId="1" shapeId="0">
+    <comment ref="J2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000006000000}">
       <text>
         <r>
           <rPr>
@@ -323,7 +337,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K2" authorId="0" shapeId="0">
+    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000007000000}">
       <text>
         <r>
           <rPr>
@@ -339,7 +353,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L2" authorId="1" shapeId="0">
+    <comment ref="L2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000008000000}">
       <text>
         <r>
           <rPr>
@@ -354,7 +368,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M2" authorId="1" shapeId="0">
+    <comment ref="M2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000009000000}">
       <text>
         <r>
           <rPr>
@@ -374,13 +388,13 @@
 </file>
 
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>YOSHIKI IWATA</author>
     <author>鈴木　大助</author>
   </authors>
   <commentList>
-    <comment ref="B6" authorId="0" shapeId="0">
+    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000001000000}">
       <text>
         <r>
           <rPr>
@@ -397,7 +411,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C9" authorId="1" shapeId="0">
+    <comment ref="C9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0600-000002000000}">
       <text>
         <r>
           <rPr>
@@ -413,7 +427,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E9" authorId="1" shapeId="0">
+    <comment ref="E9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0600-000003000000}">
       <text>
         <r>
           <rPr>
@@ -429,7 +443,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F9" authorId="1" shapeId="0">
+    <comment ref="F9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0600-000004000000}">
       <text>
         <r>
           <rPr>
@@ -444,7 +458,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G9" authorId="1" shapeId="0">
+    <comment ref="G9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0600-000005000000}">
       <text>
         <r>
           <rPr>
@@ -460,7 +474,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H9" authorId="1" shapeId="0">
+    <comment ref="H9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0600-000006000000}">
       <text>
         <r>
           <rPr>
@@ -476,7 +490,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I9" authorId="1" shapeId="0">
+    <comment ref="I9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0600-000007000000}">
       <text>
         <r>
           <rPr>
@@ -492,7 +506,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J9" authorId="1" shapeId="0">
+    <comment ref="J9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0600-000008000000}">
       <text>
         <r>
           <rPr>
@@ -512,7 +526,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2477" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2477" uniqueCount="274">
   <si>
     <t>更新履歴</t>
     <phoneticPr fontId="2"/>
@@ -2479,10 +2493,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>VSC1S95_STS</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>UNAVAILABLE</t>
   </si>
   <si>
@@ -2537,10 +2547,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>VSC1S95</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>RWT_EN</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -2566,10 +2572,6 @@
   </si>
   <si>
     <t>BAT_AO</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>VSC1S95_STS</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -2760,11 +2762,19 @@
 ・各キャプチャ画像を1A仕様書の画像に変更</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>DDM1S17_STS</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>DDM1S17</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="20">
     <font>
       <sz val="11"/>
@@ -4756,37 +4766,16 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4831,10 +4820,31 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4893,49 +4903,7 @@
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill>
@@ -4979,38 +4947,8 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFFFF00"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFF00"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FFFF0000"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFF00"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -5066,7 +5004,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="正方形/長方形 1"/>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -5855,7 +5799,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3"/>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -5899,7 +5849,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="線吹き出し 1 (枠付き) 1"/>
+        <xdr:cNvPr id="2" name="線吹き出し 1 (枠付き) 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6026,7 +5982,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="線吹き出し 1 (枠付き) 2"/>
+        <xdr:cNvPr id="3" name="線吹き出し 1 (枠付き) 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6219,7 +6181,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="図 22"/>
+        <xdr:cNvPr id="23" name="図 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000017000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -6257,7 +6225,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="図 23"/>
+        <xdr:cNvPr id="24" name="図 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000018000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -6295,7 +6269,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="正方形/長方形 24"/>
+        <xdr:cNvPr id="25" name="正方形/長方形 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000019000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6355,7 +6335,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="26" name="線吹き出し 1 (枠付き) 25"/>
+        <xdr:cNvPr id="26" name="線吹き出し 1 (枠付き) 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00001A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6438,7 +6424,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="27" name="正方形/長方形 26"/>
+        <xdr:cNvPr id="27" name="正方形/長方形 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00001B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6498,7 +6490,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="29" name="直線コネクタ 28"/>
+        <xdr:cNvPr id="29" name="直線コネクタ 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00001D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="26" idx="0"/>
           <a:endCxn id="27" idx="2"/>
@@ -6552,7 +6550,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="30" name="正方形/長方形 29"/>
+        <xdr:cNvPr id="30" name="正方形/長方形 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00001E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6612,7 +6616,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="32" name="正方形/長方形 31"/>
+        <xdr:cNvPr id="32" name="正方形/長方形 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000020000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6672,7 +6682,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="33" name="正方形/長方形 32"/>
+        <xdr:cNvPr id="33" name="正方形/長方形 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000021000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6732,7 +6748,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="35" name="線吹き出し 1 (枠付き) 34"/>
+        <xdr:cNvPr id="35" name="線吹き出し 1 (枠付き) 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000023000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6837,7 +6859,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="36" name="線吹き出し 1 (枠付き) 35"/>
+        <xdr:cNvPr id="36" name="線吹き出し 1 (枠付き) 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000024000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6920,7 +6948,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="39" name="線吹き出し 1 (枠付き) 38"/>
+        <xdr:cNvPr id="39" name="線吹き出し 1 (枠付き) 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000027000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7006,7 +7040,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="40" name="図 39"/>
+        <xdr:cNvPr id="40" name="図 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000028000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -7044,7 +7084,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="41" name="図 40"/>
+        <xdr:cNvPr id="41" name="図 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000029000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -7082,7 +7128,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="42" name="正方形/長方形 41"/>
+        <xdr:cNvPr id="42" name="正方形/長方形 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00002A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7142,7 +7194,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="43" name="正方形/長方形 42"/>
+        <xdr:cNvPr id="43" name="正方形/長方形 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00002B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7202,7 +7260,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="44" name="線吹き出し 1 (枠付き) 43"/>
+        <xdr:cNvPr id="44" name="線吹き出し 1 (枠付き) 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00002C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7296,7 +7360,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="45" name="線吹き出し 1 (枠付き) 44"/>
+        <xdr:cNvPr id="45" name="線吹き出し 1 (枠付き) 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00002D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7390,7 +7460,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4"/>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -7419,13 +7495,289 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>152231</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>91338</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>30445</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>121784</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F031124D-30F1-455B-810E-B7F299E49BF1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17394912" y="4627818"/>
+          <a:ext cx="1116359" cy="842344"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>639369</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>81190</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>20296</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>111634</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="線吹き出し 1 (枠付き) 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE8FAED9-1A0E-4397-8970-F8865D5C9E0C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10057384" y="4292910"/>
+          <a:ext cx="2253017" cy="1167102"/>
+        </a:xfrm>
+        <a:prstGeom prst="borderCallout1">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 52087"/>
+            <a:gd name="adj2" fmla="val 100142"/>
+            <a:gd name="adj3" fmla="val 67933"/>
+            <a:gd name="adj4" fmla="val 326553"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>仕様の表記が誤っているが</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>BA</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>表より以下となる。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>〇「</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>DDM1S17</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>」</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>✖「</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>VSC1S95</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>」</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -7463,9 +7815,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -7500,7 +7852,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -7535,7 +7887,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -7708,16 +8060,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B2:R13"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="1" max="1" width="4.453125" customWidth="1"/>
+    <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="2" max="2" width="9" style="10" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="69.453125" customWidth="1"/>
-    <col min="5" max="6" width="12.7265625" customWidth="1"/>
-    <col min="7" max="18" width="13.08984375" customWidth="1"/>
+    <col min="4" max="4" width="69.5" customWidth="1"/>
+    <col min="5" max="6" width="12.75" customWidth="1"/>
+    <col min="7" max="18" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="25.5" customHeight="1">
@@ -7787,7 +8139,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:18" ht="13.5" thickBot="1"/>
+    <row r="6" spans="2:18" ht="13.6" thickBot="1"/>
     <row r="7" spans="2:18">
       <c r="C7" s="222" t="s">
         <v>0</v>
@@ -7867,7 +8219,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="13.5" thickTop="1">
+    <row r="9" spans="2:18" ht="13.6" thickTop="1">
       <c r="B9" s="10">
         <f>IF(C9=0,0,ROW()-ROW($B$8))</f>
         <v>1</v>
@@ -7903,13 +8255,13 @@
         <v>31</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="N9" s="218">
         <v>43966</v>
       </c>
       <c r="O9" s="14" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="P9" s="218">
         <v>43966</v>
@@ -7921,16 +8273,16 @@
         <v>43921</v>
       </c>
     </row>
-    <row r="10" spans="2:18" ht="78">
+    <row r="10" spans="2:18" ht="77.45">
       <c r="B10" s="10">
         <f t="shared" ref="B10:B13" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
         <v>2</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D10" s="220" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>210</v>
@@ -7961,7 +8313,7 @@
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="R10" s="221">
         <v>44165</v>
@@ -8011,7 +8363,7 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="3"/>
     </row>
-    <row r="13" spans="2:18" ht="13.5" thickBot="1">
+    <row r="13" spans="2:18" ht="13.6" thickBot="1">
       <c r="B13" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8044,22 +8396,25 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <hyperlinks>
-    <hyperlink ref="I3" r:id="rId1"/>
+    <hyperlink ref="I3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:E39"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="4.6328125" customWidth="1"/>
-    <col min="3" max="3" width="3.453125" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" customWidth="1"/>
+    <col min="2" max="2" width="4.625" customWidth="1"/>
+    <col min="3" max="3" width="3.5" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
     <col min="5" max="5" width="106" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8073,13 +8428,13 @@
         <v>138</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="13.5" thickBot="1">
+    <row r="6" spans="2:5" ht="13.6" thickBot="1">
       <c r="B6" s="142" t="s">
         <v>129</v>
       </c>
       <c r="C6" s="142"/>
     </row>
-    <row r="7" spans="2:5" ht="13.5" thickBot="1">
+    <row r="7" spans="2:5" ht="13.6" thickBot="1">
       <c r="C7" s="70" t="s">
         <v>131</v>
       </c>
@@ -8099,7 +8454,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="26">
+    <row r="9" spans="2:5" ht="25.85">
       <c r="C9" s="152">
         <v>1</v>
       </c>
@@ -8110,7 +8465,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="13.5" thickBot="1">
+    <row r="10" spans="2:5" ht="13.6" thickBot="1">
       <c r="C10" s="150"/>
       <c r="D10" s="81"/>
       <c r="E10" s="6"/>
@@ -8118,14 +8473,14 @@
     <row r="11" spans="2:5">
       <c r="C11" s="148"/>
     </row>
-    <row r="12" spans="2:5" ht="13.5" thickBot="1">
+    <row r="12" spans="2:5" ht="13.6" thickBot="1">
       <c r="B12" s="143" t="s">
         <v>130</v>
       </c>
       <c r="C12" s="77"/>
       <c r="D12" s="77"/>
     </row>
-    <row r="13" spans="2:5" ht="13.5" thickBot="1">
+    <row r="13" spans="2:5" ht="13.6" thickBot="1">
       <c r="B13" s="144"/>
       <c r="C13" s="149" t="s">
         <v>131</v>
@@ -8137,7 +8492,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="13.5" thickTop="1">
+    <row r="14" spans="2:5" ht="13.6" thickTop="1">
       <c r="C14" s="146">
         <v>0</v>
       </c>
@@ -8214,17 +8569,17 @@
         <v>167</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="13.5" thickBot="1">
+    <row r="21" spans="2:5" ht="13.6" thickBot="1">
       <c r="C21" s="150"/>
       <c r="D21" s="81"/>
       <c r="E21" s="6"/>
     </row>
-    <row r="24" spans="2:5" ht="13.5" thickBot="1">
+    <row r="24" spans="2:5" ht="13.6" thickBot="1">
       <c r="B24" s="142" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="13.5" thickBot="1">
+    <row r="25" spans="2:5" ht="13.6" thickBot="1">
       <c r="C25" s="149" t="s">
         <v>131</v>
       </c>
@@ -8246,7 +8601,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="27" spans="2:5" ht="120" customHeight="1">
+    <row r="27" spans="2:5" ht="120.1" customHeight="1">
       <c r="C27" s="147">
         <v>1</v>
       </c>
@@ -8311,12 +8666,12 @@
       <c r="D33" s="80"/>
       <c r="E33" s="69"/>
     </row>
-    <row r="34" spans="2:5" ht="13.5" thickBot="1">
+    <row r="34" spans="2:5" ht="13.6" thickBot="1">
       <c r="C34" s="150"/>
       <c r="D34" s="81"/>
       <c r="E34" s="6"/>
     </row>
-    <row r="37" spans="2:5" ht="13.5" thickBot="1">
+    <row r="37" spans="2:5" ht="13.6" thickBot="1">
       <c r="B37" s="142" t="s">
         <v>163</v>
       </c>
@@ -8328,7 +8683,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="13.5" thickBot="1">
+    <row r="39" spans="2:5" ht="13.6" thickBot="1">
       <c r="C39" s="233"/>
       <c r="D39" s="234"/>
       <c r="E39" s="6" t="s">
@@ -8342,147 +8697,150 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <hyperlinks>
-    <hyperlink ref="E8" r:id="rId1"/>
-    <hyperlink ref="E9" r:id="rId2"/>
+    <hyperlink ref="E8" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="E9" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:N37"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="26.7265625" customWidth="1"/>
-    <col min="9" max="9" width="20.90625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="26.75" customWidth="1"/>
+    <col min="9" max="9" width="20.875" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="13.5" thickBot="1"/>
+    <row r="1" spans="2:14" ht="13.6" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="260" t="s">
+      <c r="B2" s="235" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="261"/>
-      <c r="D2" s="248" t="s">
-        <v>272</v>
-      </c>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="249"/>
-      <c r="H2" s="250"/>
+      <c r="C2" s="236"/>
+      <c r="D2" s="241" t="s">
+        <v>269</v>
+      </c>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="242"/>
+      <c r="H2" s="243"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="235" t="s">
+      <c r="B3" s="237" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="236"/>
-      <c r="D3" s="251" t="s">
-        <v>273</v>
-      </c>
-      <c r="E3" s="252"/>
-      <c r="F3" s="252"/>
-      <c r="G3" s="252"/>
-      <c r="H3" s="253"/>
-    </row>
-    <row r="4" spans="2:14" ht="13.5" thickBot="1">
-      <c r="B4" s="246" t="s">
+      <c r="C3" s="238"/>
+      <c r="D3" s="244" t="s">
+        <v>270</v>
+      </c>
+      <c r="E3" s="245"/>
+      <c r="F3" s="245"/>
+      <c r="G3" s="245"/>
+      <c r="H3" s="246"/>
+    </row>
+    <row r="4" spans="2:14" ht="13.6" thickBot="1">
+      <c r="B4" s="239" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="247"/>
-      <c r="D4" s="254" t="str">
+      <c r="C4" s="240"/>
+      <c r="D4" s="247" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
         <v>alert_C_VSCOFF-CSTD-0-01-A-C0.c</v>
       </c>
-      <c r="E4" s="255"/>
-      <c r="F4" s="255"/>
-      <c r="G4" s="255"/>
-      <c r="H4" s="256"/>
-    </row>
-    <row r="5" spans="2:14" ht="13.5" thickBot="1">
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="249"/>
+    </row>
+    <row r="5" spans="2:14" ht="13.6" thickBot="1">
       <c r="D5" t="str">
         <f ca="1">IF(LEN(表紙!D3&amp;".c") = LENB(表紙!D3&amp;".c"),"※モジュール名 全角チェックOK","※モジュール名 全角チェックNG：ファイル名に全角文字が使用されています！")</f>
         <v>※モジュール名 全角チェックOK</v>
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="260" t="s">
+      <c r="B6" s="235" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="261"/>
-      <c r="D6" s="257" t="str">
+      <c r="C6" s="236"/>
+      <c r="D6" s="250" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>C_VSCOFF</v>
       </c>
-      <c r="E6" s="258"/>
-      <c r="F6" s="258"/>
-      <c r="G6" s="258"/>
-      <c r="H6" s="259"/>
+      <c r="E6" s="251"/>
+      <c r="F6" s="251"/>
+      <c r="G6" s="251"/>
+      <c r="H6" s="252"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="235" t="s">
+      <c r="B7" s="237" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="236"/>
-      <c r="D7" s="237">
+      <c r="C7" s="238"/>
+      <c r="D7" s="253">
         <f>COUNTA($D$13:$D$37)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="238"/>
-      <c r="F7" s="238"/>
-      <c r="G7" s="238"/>
-      <c r="H7" s="239"/>
+      <c r="E7" s="254"/>
+      <c r="F7" s="254"/>
+      <c r="G7" s="254"/>
+      <c r="H7" s="255"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="235" t="s">
+      <c r="B8" s="237" t="s">
         <v>95</v>
       </c>
-      <c r="C8" s="236"/>
-      <c r="D8" s="237" t="str">
+      <c r="C8" s="238"/>
+      <c r="D8" s="253" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_C_VSCOFF_MTRX</v>
       </c>
-      <c r="E8" s="238"/>
-      <c r="F8" s="238"/>
-      <c r="G8" s="238"/>
-      <c r="H8" s="239"/>
+      <c r="E8" s="254"/>
+      <c r="F8" s="254"/>
+      <c r="G8" s="254"/>
+      <c r="H8" s="255"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="235" t="s">
+      <c r="B9" s="237" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="236"/>
-      <c r="D9" s="240" t="s">
+      <c r="C9" s="238"/>
+      <c r="D9" s="256" t="s">
         <v>201</v>
       </c>
-      <c r="E9" s="241"/>
-      <c r="F9" s="241"/>
-      <c r="G9" s="241"/>
-      <c r="H9" s="242"/>
-    </row>
-    <row r="10" spans="2:14" ht="13.5" thickBot="1">
-      <c r="B10" s="246" t="s">
+      <c r="E9" s="257"/>
+      <c r="F9" s="257"/>
+      <c r="G9" s="257"/>
+      <c r="H9" s="258"/>
+    </row>
+    <row r="10" spans="2:14" ht="13.6" thickBot="1">
+      <c r="B10" s="239" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="247"/>
-      <c r="D10" s="243">
+      <c r="C10" s="240"/>
+      <c r="D10" s="259">
         <v>53</v>
       </c>
-      <c r="E10" s="244"/>
-      <c r="F10" s="244"/>
-      <c r="G10" s="244"/>
-      <c r="H10" s="245"/>
-    </row>
-    <row r="11" spans="2:14" ht="13.5" thickBot="1"/>
-    <row r="12" spans="2:14" ht="13.5" thickBot="1">
+      <c r="E10" s="260"/>
+      <c r="F10" s="260"/>
+      <c r="G10" s="260"/>
+      <c r="H10" s="261"/>
+    </row>
+    <row r="11" spans="2:14" ht="13.6" thickBot="1"/>
+    <row r="12" spans="2:14" ht="13.6" thickBot="1">
       <c r="B12" s="133" t="s">
         <v>34</v>
       </c>
@@ -8517,7 +8875,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="13.5" thickTop="1">
+    <row r="13" spans="2:14" ht="13.6" thickTop="1">
       <c r="B13" s="99">
         <v>1</v>
       </c>
@@ -9370,7 +9728,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="13.5" thickBot="1">
+    <row r="37" spans="2:14" ht="13.6" thickBot="1">
       <c r="B37" s="90">
         <v>25</v>
       </c>
@@ -9411,86 +9769,79 @@
     <protectedRange sqref="D2:H3 D9:H10 C13:E37" name="編集許可"/>
   </protectedRanges>
   <mergeCells count="16">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="D9:H9"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="C15:C37">
-    <cfRule type="expression" dxfId="15" priority="9">
-      <formula>14&lt;LEN($D$6)+LEN($C15)</formula>
+  <conditionalFormatting sqref="C13:C37">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>14&lt;LEN($D$6)+LEN($C13)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5">
+    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="NG">
+      <formula>NOT(ISERROR(SEARCH("NG",D5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="14" priority="8">
+    <cfRule type="expression" dxfId="4" priority="8">
       <formula>14 &lt; LEN($D$6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D5">
-    <cfRule type="containsText" dxfId="13" priority="6" operator="containsText" text="NG">
-      <formula>NOT(ISERROR(SEARCH("NG",D5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C14">
-    <cfRule type="expression" dxfId="12" priority="4">
-      <formula>14&lt;LEN($D$6)+LEN($C14)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="11" priority="1">
-      <formula>14&lt;LEN($D$6)+LEN($C13)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E13:E37">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E13:E37" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"○,－"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D13:D37">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D13:D37" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>$K$13:$K$37</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>$L$13:$L$14</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B2:R59"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="36.453125" customWidth="1"/>
-    <col min="6" max="6" width="52.7265625" customWidth="1"/>
-    <col min="7" max="7" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="3.90625" customWidth="1"/>
-    <col min="16" max="16" width="9.90625" customWidth="1"/>
-    <col min="17" max="17" width="44.6328125" customWidth="1"/>
-    <col min="18" max="18" width="73.6328125" customWidth="1"/>
+    <col min="5" max="5" width="36.5" customWidth="1"/>
+    <col min="6" max="6" width="52.75" customWidth="1"/>
+    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="15" width="3.875" customWidth="1"/>
+    <col min="16" max="16" width="9.875" customWidth="1"/>
+    <col min="17" max="17" width="44.625" customWidth="1"/>
+    <col min="18" max="18" width="73.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="13.5" thickBot="1">
+    <row r="2" spans="2:18" ht="13.6" thickBot="1">
       <c r="B2" t="s">
         <v>188</v>
       </c>
@@ -9498,7 +9849,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="13.5" thickBot="1">
+    <row r="3" spans="2:18" ht="13.6" thickBot="1">
       <c r="B3" s="133" t="s">
         <v>34</v>
       </c>
@@ -9536,7 +9887,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="13.5" hidden="1" thickTop="1">
+    <row r="4" spans="2:18" ht="13.6" hidden="1" thickTop="1">
       <c r="B4" s="163">
         <v>0</v>
       </c>
@@ -9564,7 +9915,7 @@
       </c>
       <c r="R4" s="130"/>
     </row>
-    <row r="5" spans="2:18" ht="13.5" thickTop="1">
+    <row r="5" spans="2:18" ht="13.6" thickTop="1">
       <c r="B5" s="166">
         <v>1</v>
       </c>
@@ -10092,7 +10443,7 @@
       <c r="Q28" s="137"/>
       <c r="R28" s="107"/>
     </row>
-    <row r="29" spans="2:18" ht="13.5" thickBot="1">
+    <row r="29" spans="2:18" ht="13.6" thickBot="1">
       <c r="B29" s="167">
         <v>25</v>
       </c>
@@ -10114,7 +10465,7 @@
       <c r="Q29" s="135"/>
       <c r="R29" s="109"/>
     </row>
-    <row r="32" spans="2:18" ht="13.5" thickBot="1">
+    <row r="32" spans="2:18" ht="13.6" thickBot="1">
       <c r="B32" t="s">
         <v>189</v>
       </c>
@@ -10122,7 +10473,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="13.5" thickBot="1">
+    <row r="33" spans="2:18" ht="13.6" thickBot="1">
       <c r="B33" s="133" t="s">
         <v>34</v>
       </c>
@@ -10154,7 +10505,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="13.5" hidden="1" thickTop="1">
+    <row r="34" spans="2:18" ht="13.6" hidden="1" thickTop="1">
       <c r="B34" s="163">
         <v>0</v>
       </c>
@@ -10180,7 +10531,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="13.5" thickTop="1">
+    <row r="35" spans="2:18" ht="13.6" thickTop="1">
       <c r="B35" s="166">
         <v>1</v>
       </c>
@@ -10708,7 +11059,7 @@
       <c r="Q58" s="137"/>
       <c r="R58" s="168"/>
     </row>
-    <row r="59" spans="2:18" ht="13.5" thickBot="1">
+    <row r="59" spans="2:18" ht="13.6" thickBot="1">
       <c r="B59" s="167">
         <v>25</v>
       </c>
@@ -10737,46 +11088,49 @@
   </protectedRanges>
   <phoneticPr fontId="2"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D29">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D29" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"OPT,HW"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D35:D59">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D35:D59" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"DEF"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:U103"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="28.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.90625" customWidth="1"/>
-    <col min="5" max="5" width="12.36328125" customWidth="1"/>
-    <col min="6" max="6" width="19.7265625" customWidth="1"/>
-    <col min="7" max="7" width="12.36328125" customWidth="1"/>
+    <col min="2" max="2" width="28.375" customWidth="1"/>
+    <col min="3" max="3" width="15.875" customWidth="1"/>
+    <col min="5" max="5" width="12.375" customWidth="1"/>
+    <col min="6" max="6" width="19.75" customWidth="1"/>
+    <col min="7" max="7" width="12.375" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="11" width="12.36328125" customWidth="1"/>
-    <col min="12" max="12" width="16.08984375" customWidth="1"/>
-    <col min="14" max="14" width="30.08984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="57.08984375" hidden="1" customWidth="1"/>
+    <col min="9" max="11" width="12.375" customWidth="1"/>
+    <col min="12" max="12" width="16.125" customWidth="1"/>
+    <col min="14" max="14" width="30.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="57.125" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="13.5" thickBot="1">
+    <row r="1" spans="2:21" ht="13.6" thickBot="1">
       <c r="C1" s="83" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="13.5" thickBot="1">
+    <row r="2" spans="2:21" ht="13.6" thickBot="1">
       <c r="B2" s="91" t="s">
         <v>58</v>
       </c>
@@ -10820,7 +11174,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="14" hidden="1" thickTop="1" thickBot="1">
+    <row r="3" spans="2:21" ht="14.3" hidden="1" thickTop="1" thickBot="1">
       <c r="B3" s="25"/>
       <c r="C3" s="45" t="s">
         <v>108</v>
@@ -10841,7 +11195,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="13.5" thickTop="1">
+    <row r="4" spans="2:21" ht="13.6" thickTop="1">
       <c r="B4" s="102" t="s">
         <v>212</v>
       </c>
@@ -10852,7 +11206,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="179" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F4" s="180" t="s">
         <v>214</v>
@@ -11109,7 +11463,7 @@
       </c>
       <c r="U12" s="29"/>
     </row>
-    <row r="13" spans="2:21" ht="13.5" thickBot="1">
+    <row r="13" spans="2:21" ht="13.6" thickBot="1">
       <c r="B13" s="102"/>
       <c r="C13" s="101"/>
       <c r="D13" s="111"/>
@@ -13360,7 +13714,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="2:15" ht="13.5" thickBot="1">
+    <row r="103" spans="2:15" ht="13.6" thickBot="1">
       <c r="B103" s="47"/>
       <c r="C103" s="48"/>
       <c r="D103" s="108"/>
@@ -13391,33 +13745,31 @@
     <protectedRange sqref="B4:L103" name="範囲1"/>
   </protectedRanges>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="M4:M103">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="greaterThan">
-      <formula>32</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M3">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="greaterThan">
+  <conditionalFormatting sqref="M3:M103">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
       <formula>32</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3 G3 I3 E3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3 G3 I3 E3" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"あり,なし"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <legacyDrawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0400-000001000000}">
           <x14:formula1>
             <xm:f>Matrix!$H$13:$H$37</xm:f>
           </x14:formula1>
           <xm:sqref>B3:B103</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0400-000002000000}">
           <x14:formula1>
             <xm:f>Config_IF!$C$4:$C$29</xm:f>
           </x14:formula1>
@@ -13430,23 +13782,23 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FFCCECFF"/>
   </sheetPr>
   <dimension ref="A1:AW199"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
     <col min="4" max="35" width="3" customWidth="1"/>
-    <col min="36" max="36" width="36.36328125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.08984375" customWidth="1"/>
+    <col min="36" max="36" width="36.375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.125" customWidth="1"/>
     <col min="38" max="42" width="9" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="20.6328125" hidden="1" customWidth="1"/>
-    <col min="44" max="47" width="41.08984375" customWidth="1"/>
-    <col min="48" max="48" width="23.6328125" customWidth="1"/>
+    <col min="43" max="43" width="20.625" hidden="1" customWidth="1"/>
+    <col min="44" max="47" width="41.125" customWidth="1"/>
+    <col min="48" max="48" width="23.625" customWidth="1"/>
     <col min="49" max="49" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -13565,7 +13917,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="3" spans="1:49" ht="213" customHeight="1" thickBot="1">
+    <row r="3" spans="1:49" ht="212.95" customHeight="1" thickBot="1">
       <c r="B3" s="219" t="str">
         <f>IF(OR(IF(COUNTIF(D6:AC69,"0")&lt;&gt;0,TRUE,FALSE),IF(COUNTIF(D6:AC69,"1")&lt;&gt;0,TRUE,FALSE)),"Search Table","Index Table")</f>
         <v>Index Table</v>
@@ -13659,10 +14011,10 @@
         <v>203</v>
       </c>
       <c r="AG3" s="200" t="s">
-        <v>216</v>
+        <v>272</v>
       </c>
       <c r="AH3" s="270" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AI3" s="271"/>
       <c r="AJ3" s="265"/>
@@ -13670,7 +14022,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="13.5" thickBot="1">
+    <row r="4" spans="1:49" ht="13.6" thickBot="1">
       <c r="A4" s="266" t="s">
         <v>63</v>
       </c>
@@ -13718,7 +14070,7 @@
       <c r="AV4" s="73"/>
       <c r="AW4" s="74"/>
     </row>
-    <row r="5" spans="1:49" ht="13.5" thickBot="1">
+    <row r="5" spans="1:49" ht="13.6" thickBot="1">
       <c r="A5" s="268"/>
       <c r="B5" s="269"/>
       <c r="C5" s="128"/>
@@ -14281,7 +14633,7 @@
         <v>1</v>
       </c>
       <c r="AJ9" s="45" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AL9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -15229,7 +15581,7 @@
         <v>ALERT_VOM_IGN_ON</v>
       </c>
     </row>
-    <row r="17" spans="2:49" ht="13.5" thickBot="1">
+    <row r="17" spans="2:49" ht="13.6" thickBot="1">
       <c r="B17" s="124"/>
       <c r="C17" s="41">
         <f t="shared" si="2"/>
@@ -21599,7 +21951,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="13.5" thickBot="1">
+    <row r="70" spans="1:46" ht="13.6" thickBot="1">
       <c r="A70" s="50" t="s">
         <v>64</v>
       </c>
@@ -42195,49 +42547,28 @@
     <mergeCell ref="AH3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="D34:AI69 D10:AE33">
-    <cfRule type="cellIs" dxfId="8" priority="34" operator="equal">
+  <conditionalFormatting sqref="D6:AI69">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"×"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AR5:AS70">
-    <cfRule type="expression" dxfId="6" priority="33">
+    <cfRule type="expression" dxfId="0" priority="33">
       <formula>$B$3="Index Table"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D6:AE9">
-    <cfRule type="cellIs" dxfId="5" priority="21" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="22" operator="equal">
-      <formula>"×"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF14:AI33 AF6:AF13">
-    <cfRule type="cellIs" dxfId="3" priority="9" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="10" operator="equal">
-      <formula>"×"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG6:AI13">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
-      <formula>"×"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0500-000000000000}">
           <x14:formula1>
             <xm:f>CH_Design!$C$3:$C$103</xm:f>
           </x14:formula1>
@@ -42250,27 +42581,27 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:Q15"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="35.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="10" width="3.36328125" customWidth="1"/>
-    <col min="11" max="11" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="10.90625" customWidth="1"/>
+    <col min="2" max="2" width="35.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="3.375" customWidth="1"/>
+    <col min="11" max="11" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" ht="14.5" thickBot="1">
+    <row r="2" spans="2:17" ht="15.65" thickBot="1">
       <c r="B2" s="26" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3" spans="2:17" ht="15.65" thickBot="1">
+      <c r="B3" s="88" t="s">
         <v>218</v>
-      </c>
-    </row>
-    <row r="3" spans="2:17" ht="14.5" thickBot="1">
-      <c r="B3" s="88" t="s">
-        <v>219</v>
       </c>
       <c r="C3" s="272" t="s">
         <v>202</v>
@@ -42293,7 +42624,7 @@
     <row r="4" spans="2:17">
       <c r="B4" s="64"/>
       <c r="C4" s="32" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D4" s="32"/>
       <c r="E4" s="32"/>
@@ -42305,7 +42636,7 @@
       <c r="K4" s="32"/>
       <c r="L4" s="201"/>
       <c r="M4" s="28" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="N4" s="37" t="s">
         <v>21</v>
@@ -42319,7 +42650,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="275" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D5" s="276"/>
       <c r="E5" s="276"/>
@@ -42333,7 +42664,7 @@
       </c>
       <c r="L5" s="202"/>
       <c r="M5" s="29" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N5" s="203" t="s">
         <v>23</v>
@@ -42353,28 +42684,28 @@
         <v>33</v>
       </c>
       <c r="C6" s="155" t="s">
+        <v>223</v>
+      </c>
+      <c r="D6" s="155" t="s">
         <v>224</v>
       </c>
-      <c r="D6" s="155" t="s">
+      <c r="E6" s="155" t="s">
         <v>225</v>
       </c>
-      <c r="E6" s="155" t="s">
+      <c r="F6" s="155" t="s">
         <v>226</v>
       </c>
-      <c r="F6" s="155" t="s">
-        <v>227</v>
-      </c>
       <c r="G6" s="155" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H6" s="155" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I6" s="155" t="s">
+        <v>225</v>
+      </c>
+      <c r="J6" s="155" t="s">
         <v>226</v>
-      </c>
-      <c r="J6" s="155" t="s">
-        <v>227</v>
       </c>
       <c r="K6" s="129" t="s">
         <v>209</v>
@@ -42383,19 +42714,19 @@
         <v>209</v>
       </c>
       <c r="M6" s="29" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="N6" s="205"/>
       <c r="O6" s="194"/>
       <c r="P6" s="194"/>
       <c r="Q6" s="130"/>
     </row>
-    <row r="7" spans="2:17" ht="26">
+    <row r="7" spans="2:17" ht="25.85">
       <c r="B7" s="66" t="s">
         <v>27</v>
       </c>
       <c r="C7" s="278" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D7" s="276"/>
       <c r="E7" s="276"/>
@@ -42405,10 +42736,10 @@
       <c r="I7" s="276"/>
       <c r="J7" s="277"/>
       <c r="K7" s="1" t="s">
-        <v>230</v>
+        <v>273</v>
       </c>
       <c r="L7" s="206" t="s">
-        <v>230</v>
+        <v>273</v>
       </c>
       <c r="M7" s="30"/>
       <c r="N7" s="205"/>
@@ -42416,39 +42747,39 @@
       <c r="P7" s="194"/>
       <c r="Q7" s="130"/>
     </row>
-    <row r="8" spans="2:17" ht="62">
+    <row r="8" spans="2:17" ht="61.15">
       <c r="B8" s="65" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="207" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D8" s="207" t="s">
         <v>62</v>
       </c>
       <c r="E8" s="207" t="s">
+        <v>230</v>
+      </c>
+      <c r="F8" s="207" t="s">
+        <v>231</v>
+      </c>
+      <c r="G8" s="207" t="s">
         <v>232</v>
       </c>
-      <c r="F8" s="207" t="s">
+      <c r="H8" s="207" t="s">
         <v>233</v>
       </c>
-      <c r="G8" s="207" t="s">
+      <c r="I8" s="207" t="s">
         <v>234</v>
       </c>
-      <c r="H8" s="207" t="s">
+      <c r="J8" s="207" t="s">
         <v>235</v>
       </c>
-      <c r="I8" s="207" t="s">
-        <v>236</v>
-      </c>
-      <c r="J8" s="207" t="s">
-        <v>237</v>
-      </c>
       <c r="K8" s="1" t="s">
-        <v>238</v>
+        <v>272</v>
       </c>
       <c r="L8" s="206" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="M8" s="29" t="s">
         <v>29</v>
@@ -42463,48 +42794,48 @@
         <v>30</v>
       </c>
       <c r="C9" s="156" t="s">
+        <v>236</v>
+      </c>
+      <c r="D9" s="156" t="s">
+        <v>225</v>
+      </c>
+      <c r="E9" s="156" t="s">
+        <v>237</v>
+      </c>
+      <c r="F9" s="156" t="s">
+        <v>238</v>
+      </c>
+      <c r="G9" s="156" t="s">
+        <v>236</v>
+      </c>
+      <c r="H9" s="156" t="s">
+        <v>236</v>
+      </c>
+      <c r="I9" s="156" t="s">
+        <v>238</v>
+      </c>
+      <c r="J9" s="156" t="s">
+        <v>236</v>
+      </c>
+      <c r="K9" s="27" t="s">
         <v>239</v>
       </c>
-      <c r="D9" s="156" t="s">
-        <v>226</v>
-      </c>
-      <c r="E9" s="156" t="s">
+      <c r="L9" s="208" t="s">
         <v>240</v>
       </c>
-      <c r="F9" s="156" t="s">
+      <c r="M9" s="31" t="s">
         <v>241</v>
       </c>
-      <c r="G9" s="156" t="s">
-        <v>239</v>
-      </c>
-      <c r="H9" s="156" t="s">
-        <v>239</v>
-      </c>
-      <c r="I9" s="156" t="s">
-        <v>241</v>
-      </c>
-      <c r="J9" s="156" t="s">
-        <v>239</v>
-      </c>
-      <c r="K9" s="27" t="s">
+      <c r="N9" s="209" t="s">
         <v>242</v>
-      </c>
-      <c r="L9" s="208" t="s">
-        <v>243</v>
-      </c>
-      <c r="M9" s="31" t="s">
-        <v>244</v>
-      </c>
-      <c r="N9" s="209" t="s">
-        <v>245</v>
       </c>
       <c r="O9" s="199"/>
       <c r="P9" s="210"/>
       <c r="Q9" s="131"/>
     </row>
-    <row r="10" spans="2:17" ht="13.5" thickTop="1">
+    <row r="10" spans="2:17" ht="13.6" thickTop="1">
       <c r="B10" s="68" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C10" s="157" t="s">
         <v>160</v>
@@ -42531,13 +42862,13 @@
         <v>160</v>
       </c>
       <c r="K10" s="34" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="L10" s="211" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="M10" s="35" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N10" s="212" t="s">
         <v>31</v>
@@ -42548,7 +42879,7 @@
     </row>
     <row r="11" spans="2:17">
       <c r="B11" s="213" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C11" s="158" t="s">
         <v>160</v>
@@ -42575,16 +42906,16 @@
         <v>160</v>
       </c>
       <c r="K11" s="198" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="L11" s="214" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="M11" s="36" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N11" s="215" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O11" s="196"/>
       <c r="P11" s="196"/>
@@ -42592,7 +42923,7 @@
     </row>
     <row r="12" spans="2:17">
       <c r="B12" s="213" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C12" s="158" t="s">
         <v>160</v>
@@ -42619,16 +42950,16 @@
         <v>160</v>
       </c>
       <c r="K12" s="198" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="L12" s="214" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M12" s="36" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N12" s="215" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O12" s="196"/>
       <c r="P12" s="196"/>
@@ -42636,7 +42967,7 @@
     </row>
     <row r="13" spans="2:17">
       <c r="B13" s="213" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C13" s="158" t="s">
         <v>160</v>
@@ -42663,16 +42994,16 @@
         <v>160</v>
       </c>
       <c r="K13" s="198" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="L13" s="214" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="M13" s="36" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="N13" s="215" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="O13" s="196"/>
       <c r="P13" s="196"/>
@@ -42680,7 +43011,7 @@
     </row>
     <row r="14" spans="2:17">
       <c r="B14" s="213" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C14" s="158" t="s">
         <v>160</v>
@@ -42707,24 +43038,24 @@
         <v>160</v>
       </c>
       <c r="K14" s="198" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="L14" s="214" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="M14" s="36" t="s">
         <v>32</v>
       </c>
       <c r="N14" s="215" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O14" s="196"/>
       <c r="P14" s="196"/>
       <c r="Q14" s="132"/>
     </row>
-    <row r="15" spans="2:17" ht="13.5" thickBot="1">
+    <row r="15" spans="2:17" ht="13.6" thickBot="1">
       <c r="B15" s="183" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C15" s="184" t="s">
         <v>160</v>
@@ -42751,10 +43082,10 @@
         <v>160</v>
       </c>
       <c r="K15" s="185" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L15" s="216" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="M15" s="186" t="s">
         <v>32</v>
@@ -42774,28 +43105,31 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3" xr:uid="{00000000-0002-0000-0600-000000000000}">
       <formula1>"Index,Matrix Search"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:D27"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="4.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.26953125" customWidth="1"/>
+    <col min="2" max="2" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.25" customWidth="1"/>
     <col min="4" max="4" width="86" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="13.5" thickBot="1">
+    <row r="2" spans="2:4" ht="13.6" thickBot="1">
       <c r="B2" s="76" t="s">
         <v>85</v>
       </c>
@@ -42805,7 +43139,7 @@
       </c>
       <c r="D2" s="77"/>
     </row>
-    <row r="3" spans="2:4" ht="13.5" thickBot="1">
+    <row r="3" spans="2:4" ht="13.6" thickBot="1">
       <c r="B3" s="70" t="s">
         <v>85</v>
       </c>
@@ -42816,7 +43150,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="13.5" thickTop="1">
+    <row r="4" spans="2:4" ht="13.6" thickTop="1">
       <c r="B4" s="13">
         <v>0</v>
       </c>
@@ -42827,7 +43161,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="39">
+    <row r="5" spans="2:4" ht="38.75">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -42838,7 +43172,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="26">
+    <row r="6" spans="2:4" ht="25.85">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -42849,7 +43183,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="52">
+    <row r="7" spans="2:4" ht="51.65">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -42860,7 +43194,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="78">
+    <row r="8" spans="2:4" ht="77.45">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -42871,7 +43205,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="41.25" customHeight="1">
+    <row r="9" spans="2:4" ht="41.3" customHeight="1">
       <c r="B9" s="2">
         <v>5</v>
       </c>
@@ -42882,7 +43216,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="26">
+    <row r="10" spans="2:4" ht="25.85">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -42893,7 +43227,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="26">
+    <row r="11" spans="2:4" ht="25.85">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -42904,7 +43238,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="26">
+    <row r="12" spans="2:4" ht="25.85">
       <c r="B12" s="2">
         <v>8</v>
       </c>
@@ -42915,7 +43249,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="26">
+    <row r="13" spans="2:4" ht="25.85">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -42926,7 +43260,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="26">
+    <row r="14" spans="2:4" ht="25.85">
       <c r="B14" s="2">
         <v>10</v>
       </c>
@@ -42937,7 +43271,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="130">
+    <row r="15" spans="2:4" ht="129.1">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -42959,7 +43293,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="26">
+    <row r="17" spans="2:4" ht="25.85">
       <c r="B17" s="2">
         <v>13</v>
       </c>
@@ -42970,7 +43304,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="91">
+    <row r="18" spans="2:4" ht="90.35">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -42981,7 +43315,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="39">
+    <row r="19" spans="2:4" ht="38.75">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -42992,7 +43326,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="20" spans="2:4" ht="64.5" customHeight="1">
+    <row r="20" spans="2:4" ht="64.55" customHeight="1">
       <c r="B20" s="2">
         <v>16</v>
       </c>
@@ -43014,26 +43348,26 @@
         <v>192</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="26">
+    <row r="22" spans="2:4" ht="25.85">
       <c r="B22" s="2">
         <v>18</v>
       </c>
       <c r="C22" s="80" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D22" s="82" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" ht="26">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="25.85">
       <c r="B23" s="2">
         <v>19</v>
       </c>
       <c r="C23" s="80" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D23" s="82" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="24" spans="2:4">
@@ -43051,7 +43385,7 @@
       <c r="C26" s="80"/>
       <c r="D26" s="69"/>
     </row>
-    <row r="27" spans="2:4" ht="13.5" thickBot="1">
+    <row r="27" spans="2:4" ht="13.6" thickBot="1">
       <c r="B27" s="4"/>
       <c r="C27" s="81"/>
       <c r="D27" s="6"/>
@@ -43060,5 +43394,8 @@
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>